--- a/01_My_Learnings/05_NSO_work/Meta_Data.xlsx
+++ b/01_My_Learnings/05_NSO_work/Meta_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\01_My_Learnings\05_NSO_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C881DF98-54A1-48EB-845A-A046D273E509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C99B006-F5E6-4312-B55E-B3E92837322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>crop_cd</t>
   </si>
@@ -722,7 +722,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -742,7 +742,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -750,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -758,7 +758,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -766,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -774,7 +774,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -798,7 +798,7 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -806,15 +806,15 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>3</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -830,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -838,7 +838,7 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -846,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -862,7 +862,7 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -878,22 +878,6 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21">
         <v>92</v>
       </c>
     </row>
@@ -956,264 +940,231 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>40</v>
+      </c>
+      <c r="F2">
+        <v>0.24364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>40</v>
+      </c>
+      <c r="F3">
+        <v>0.28720000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="F4">
+        <v>0.31452000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>40</v>
-      </c>
-      <c r="F2">
-        <v>40</v>
-      </c>
-      <c r="G2">
-        <v>0.24364</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+      <c r="F5">
+        <v>0.29511999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>6.59E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>40</v>
-      </c>
-      <c r="F3">
-        <v>40</v>
-      </c>
-      <c r="G3">
-        <v>0.28720000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>40</v>
-      </c>
-      <c r="G4">
-        <v>0.31452000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>40</v>
-      </c>
-      <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5">
-        <v>0.29511999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <v>40</v>
-      </c>
-      <c r="G7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>6.59E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>40</v>
-      </c>
-      <c r="F9">
-        <v>40</v>
-      </c>
-      <c r="G9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
+      <c r="D10">
+        <v>40</v>
       </c>
       <c r="E10">
         <v>40</v>
       </c>
       <c r="F10">
-        <v>40</v>
-      </c>
-      <c r="G10">
         <v>0.24939913599999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
         <v>92</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C11" t="s">
         <v>13</v>
+      </c>
+      <c r="D11">
+        <v>60</v>
       </c>
       <c r="E11">
         <v>60</v>
       </c>
       <c r="F11">
-        <v>60</v>
-      </c>
-      <c r="G11">
         <v>0.24865243200000001</v>
       </c>
     </row>
